--- a/MainTop/06.10.2026 Макс ВБ/print_print_sorted.xlsx
+++ b/MainTop/06.10.2026 Макс ВБ/print_print_sorted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\06.10.2026 Макс ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F8F15E-6C43-4D09-A327-9627A5C8D70B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A78F8D0-C122-4857-A647-B70D62316811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -407,7 +407,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -444,6 +444,54 @@
         <bgColor rgb="FFFFA07A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FFFFFF99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF99CCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor rgb="FF99CCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor rgb="FFFFCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor rgb="FFCCFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FFCCFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFFA07A"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -472,7 +520,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -485,6 +533,14 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -808,10 +864,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="7">
+      <c r="A2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="12">
         <v>52</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -823,10 +879,10 @@
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="12">
         <v>40</v>
       </c>
       <c r="C3" s="7" t="s">
@@ -838,10 +894,10 @@
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="7">
+      <c r="A4" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="12">
         <v>28</v>
       </c>
       <c r="C4" s="7" t="s">
@@ -853,10 +909,10 @@
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="12">
         <v>20</v>
       </c>
       <c r="C5" s="7" t="s">
@@ -868,10 +924,10 @@
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="12">
         <v>20</v>
       </c>
       <c r="C6" s="7" t="s">
@@ -883,10 +939,10 @@
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="12">
         <v>20</v>
       </c>
       <c r="C7" s="7" t="s">
@@ -898,10 +954,10 @@
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="12">
         <v>16</v>
       </c>
       <c r="C8" s="7" t="s">
@@ -913,10 +969,10 @@
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="12">
         <v>12</v>
       </c>
       <c r="C9" s="7" t="s">
@@ -928,10 +984,10 @@
       <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="12">
         <v>12</v>
       </c>
       <c r="C10" s="7" t="s">
@@ -943,10 +999,10 @@
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="12">
         <v>8</v>
       </c>
       <c r="C11" s="7" t="s">
@@ -958,10 +1014,10 @@
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="12">
         <v>8</v>
       </c>
       <c r="C12" s="7" t="s">
@@ -973,10 +1029,10 @@
       <c r="E12" s="1"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="12">
         <v>8</v>
       </c>
       <c r="C13" s="7" t="s">
@@ -988,10 +1044,10 @@
       <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="12">
         <v>8</v>
       </c>
       <c r="C14" s="7" t="s">
@@ -1003,10 +1059,10 @@
       <c r="E14" s="1"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="13">
         <v>8</v>
       </c>
       <c r="C15" s="7" t="s">
@@ -1018,10 +1074,10 @@
       <c r="E15" s="1"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="13">
         <v>8</v>
       </c>
       <c r="C16" s="7" t="s">
@@ -1033,10 +1089,10 @@
       <c r="E16" s="1"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="13">
         <v>8</v>
       </c>
       <c r="C17" s="7" t="s">
@@ -1048,10 +1104,10 @@
       <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="13">
         <v>4</v>
       </c>
       <c r="C18" s="7" t="s">
@@ -1063,10 +1119,10 @@
       <c r="E18" s="1"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="13">
         <v>4</v>
       </c>
       <c r="C19" s="7" t="s">
@@ -1078,10 +1134,10 @@
       <c r="E19" s="1"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="13">
         <v>4</v>
       </c>
       <c r="C20" s="7" t="s">
@@ -1093,10 +1149,10 @@
       <c r="E20" s="1"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="13">
         <v>4</v>
       </c>
       <c r="C21" s="7" t="s">
@@ -1108,10 +1164,10 @@
       <c r="E21" s="1"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="13">
         <v>4</v>
       </c>
       <c r="C22" s="7" t="s">
@@ -1123,10 +1179,10 @@
       <c r="E22" s="1"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="13">
         <v>4</v>
       </c>
       <c r="C23" s="7" t="s">
@@ -1138,10 +1194,10 @@
       <c r="E23" s="1"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="13">
         <v>4</v>
       </c>
       <c r="C24" s="7" t="s">
@@ -1153,10 +1209,10 @@
       <c r="E24" s="1"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="13">
         <v>4</v>
       </c>
       <c r="C25" s="7" t="s">
@@ -1168,10 +1224,10 @@
       <c r="E25" s="1"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="13">
         <v>4</v>
       </c>
       <c r="C26" s="7" t="s">
@@ -1183,10 +1239,10 @@
       <c r="E26" s="1"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="13">
         <v>4</v>
       </c>
       <c r="C27" s="7" t="s">
@@ -1198,10 +1254,10 @@
       <c r="E27" s="1"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="13">
         <v>4</v>
       </c>
       <c r="C28" s="7" t="s">
@@ -1213,10 +1269,10 @@
       <c r="E28" s="1"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="13">
         <v>4</v>
       </c>
       <c r="C29" s="7" t="s">
@@ -1228,10 +1284,10 @@
       <c r="E29" s="1"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="13">
         <v>4</v>
       </c>
       <c r="C30" s="7" t="s">
@@ -1243,10 +1299,10 @@
       <c r="E30" s="1"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="13">
         <v>4</v>
       </c>
       <c r="C31" s="7" t="s">
@@ -1258,10 +1314,10 @@
       <c r="E31" s="1"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="13">
         <v>4</v>
       </c>
       <c r="C32" s="7" t="s">
@@ -1273,10 +1329,10 @@
       <c r="E32" s="1"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="13">
         <v>4</v>
       </c>
       <c r="C33" s="7" t="s">
@@ -1288,10 +1344,10 @@
       <c r="E33" s="1"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="13">
         <v>4</v>
       </c>
       <c r="C34" s="7" t="s">
@@ -1303,10 +1359,10 @@
       <c r="E34" s="1"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="13">
         <v>4</v>
       </c>
       <c r="C35" s="7" t="s">
@@ -1318,10 +1374,10 @@
       <c r="E35" s="1"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B36" s="14">
         <v>4</v>
       </c>
       <c r="C36" s="8" t="s">
@@ -1333,10 +1389,10 @@
       <c r="E36" s="2"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="8">
+      <c r="B37" s="14">
         <v>4</v>
       </c>
       <c r="C37" s="8" t="s">
@@ -1348,10 +1404,10 @@
       <c r="E37" s="2"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="8">
+      <c r="B38" s="14">
         <v>4</v>
       </c>
       <c r="C38" s="8" t="s">
@@ -1363,10 +1419,10 @@
       <c r="E38" s="2"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B39" s="8">
+      <c r="B39" s="14">
         <v>4</v>
       </c>
       <c r="C39" s="8" t="s">
@@ -1378,10 +1434,10 @@
       <c r="E39" s="2"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="8">
+      <c r="B40" s="14">
         <v>4</v>
       </c>
       <c r="C40" s="8" t="s">
@@ -1393,10 +1449,10 @@
       <c r="E40" s="2"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B41" s="8">
+      <c r="B41" s="14">
         <v>2</v>
       </c>
       <c r="C41" s="8" t="s">
@@ -1408,10 +1464,10 @@
       <c r="E41" s="2"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B42" s="8">
+      <c r="B42" s="14">
         <v>2</v>
       </c>
       <c r="C42" s="8" t="s">
@@ -1423,10 +1479,10 @@
       <c r="E42" s="2"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="B43" s="8">
+      <c r="B43" s="14">
         <v>2</v>
       </c>
       <c r="C43" s="8" t="s">
@@ -1438,10 +1494,10 @@
       <c r="E43" s="2"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B44" s="8">
+      <c r="B44" s="14">
         <v>2</v>
       </c>
       <c r="C44" s="8" t="s">
@@ -1453,10 +1509,10 @@
       <c r="E44" s="2"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="B45" s="8">
+      <c r="B45" s="14">
         <v>2</v>
       </c>
       <c r="C45" s="8" t="s">
@@ -1468,10 +1524,10 @@
       <c r="E45" s="2"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="B46" s="8">
+      <c r="B46" s="14">
         <v>44</v>
       </c>
       <c r="C46" s="8" t="s">
@@ -1483,10 +1539,10 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B47" s="8">
+      <c r="B47" s="14">
         <v>24</v>
       </c>
       <c r="C47" s="8" t="s">
@@ -1498,10 +1554,10 @@
       <c r="E47" s="2"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="B48" s="8">
+      <c r="B48" s="14">
         <v>24</v>
       </c>
       <c r="C48" s="8" t="s">
@@ -1513,10 +1569,10 @@
       <c r="E48" s="2"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B49" s="8">
+      <c r="B49" s="14">
         <v>24</v>
       </c>
       <c r="C49" s="8" t="s">
@@ -1528,10 +1584,10 @@
       <c r="E49" s="2"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B50" s="8">
+      <c r="B50" s="14">
         <v>20</v>
       </c>
       <c r="C50" s="8" t="s">
@@ -1543,10 +1599,10 @@
       <c r="E50" s="2"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B51" s="8">
+      <c r="B51" s="14">
         <v>20</v>
       </c>
       <c r="C51" s="8" t="s">
@@ -1558,10 +1614,10 @@
       <c r="E51" s="2"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="B52" s="8">
+      <c r="B52" s="14">
         <v>16</v>
       </c>
       <c r="C52" s="8" t="s">
@@ -1573,10 +1629,10 @@
       <c r="E52" s="2"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="B53" s="8">
+      <c r="B53" s="14">
         <v>16</v>
       </c>
       <c r="C53" s="8" t="s">
@@ -1588,10 +1644,10 @@
       <c r="E53" s="2"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B54" s="8">
+      <c r="B54" s="14">
         <v>16</v>
       </c>
       <c r="C54" s="8" t="s">
@@ -1603,10 +1659,10 @@
       <c r="E54" s="2"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B55" s="8">
+      <c r="B55" s="14">
         <v>12</v>
       </c>
       <c r="C55" s="8" t="s">
@@ -1618,10 +1674,10 @@
       <c r="E55" s="2"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B56" s="8">
+      <c r="B56" s="14">
         <v>12</v>
       </c>
       <c r="C56" s="8" t="s">
@@ -1633,10 +1689,10 @@
       <c r="E56" s="2"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="B57" s="8">
+      <c r="B57" s="15">
         <v>12</v>
       </c>
       <c r="C57" s="8" t="s">
@@ -1648,10 +1704,10 @@
       <c r="E57" s="2"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B58" s="8">
+      <c r="B58" s="15">
         <v>12</v>
       </c>
       <c r="C58" s="8" t="s">
@@ -1663,10 +1719,10 @@
       <c r="E58" s="2"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="B59" s="8">
+      <c r="B59" s="15">
         <v>12</v>
       </c>
       <c r="C59" s="8" t="s">
@@ -1678,10 +1734,10 @@
       <c r="E59" s="2"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="B60" s="8">
+      <c r="B60" s="15">
         <v>12</v>
       </c>
       <c r="C60" s="8" t="s">
@@ -1693,10 +1749,10 @@
       <c r="E60" s="2"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="B61" s="8">
+      <c r="B61" s="15">
         <v>8</v>
       </c>
       <c r="C61" s="8" t="s">
@@ -1708,10 +1764,10 @@
       <c r="E61" s="2"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="B62" s="8">
+      <c r="B62" s="15">
         <v>8</v>
       </c>
       <c r="C62" s="8" t="s">
@@ -1723,10 +1779,10 @@
       <c r="E62" s="2"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="B63" s="8">
+      <c r="B63" s="15">
         <v>8</v>
       </c>
       <c r="C63" s="8" t="s">
@@ -1738,10 +1794,10 @@
       <c r="E63" s="2"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="8" t="s">
+      <c r="A64" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="B64" s="8">
+      <c r="B64" s="15">
         <v>8</v>
       </c>
       <c r="C64" s="8" t="s">
@@ -1753,10 +1809,10 @@
       <c r="E64" s="2"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="B65" s="8">
+      <c r="B65" s="15">
         <v>8</v>
       </c>
       <c r="C65" s="8" t="s">
@@ -1768,10 +1824,10 @@
       <c r="E65" s="2"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="9" t="s">
+      <c r="A66" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="B66" s="9">
+      <c r="B66" s="16">
         <v>8</v>
       </c>
       <c r="C66" s="9" t="s">
@@ -1783,10 +1839,10 @@
       <c r="E66" s="3"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="9" t="s">
+      <c r="A67" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="B67" s="9">
+      <c r="B67" s="16">
         <v>8</v>
       </c>
       <c r="C67" s="9" t="s">
@@ -1798,10 +1854,10 @@
       <c r="E67" s="3"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="9" t="s">
+      <c r="A68" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="B68" s="9">
+      <c r="B68" s="16">
         <v>8</v>
       </c>
       <c r="C68" s="9" t="s">
@@ -1813,10 +1869,10 @@
       <c r="E68" s="3"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="9" t="s">
+      <c r="A69" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="B69" s="9">
+      <c r="B69" s="16">
         <v>8</v>
       </c>
       <c r="C69" s="9" t="s">
@@ -1828,10 +1884,10 @@
       <c r="E69" s="3"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="9" t="s">
+      <c r="A70" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="B70" s="9">
+      <c r="B70" s="16">
         <v>8</v>
       </c>
       <c r="C70" s="9" t="s">
@@ -1843,10 +1899,10 @@
       <c r="E70" s="3"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="9" t="s">
+      <c r="A71" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="B71" s="9">
+      <c r="B71" s="16">
         <v>8</v>
       </c>
       <c r="C71" s="9" t="s">
@@ -1858,10 +1914,10 @@
       <c r="E71" s="3"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="9" t="s">
+      <c r="A72" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="B72" s="9">
+      <c r="B72" s="16">
         <v>8</v>
       </c>
       <c r="C72" s="9" t="s">
@@ -1873,10 +1929,10 @@
       <c r="E72" s="3"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="9" t="s">
+      <c r="A73" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="B73" s="9">
+      <c r="B73" s="16">
         <v>8</v>
       </c>
       <c r="C73" s="9" t="s">
@@ -1888,10 +1944,10 @@
       <c r="E73" s="3"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="9" t="s">
+      <c r="A74" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="B74" s="9">
+      <c r="B74" s="16">
         <v>8</v>
       </c>
       <c r="C74" s="9" t="s">
@@ -1903,10 +1959,10 @@
       <c r="E74" s="3"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="9" t="s">
+      <c r="A75" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="B75" s="9">
+      <c r="B75" s="16">
         <v>8</v>
       </c>
       <c r="C75" s="9" t="s">
@@ -1918,10 +1974,10 @@
       <c r="E75" s="3"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="9" t="s">
+      <c r="A76" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="B76" s="9">
+      <c r="B76" s="16">
         <v>8</v>
       </c>
       <c r="C76" s="9" t="s">
@@ -1933,10 +1989,10 @@
       <c r="E76" s="3"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="9" t="s">
+      <c r="A77" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="B77" s="9">
+      <c r="B77" s="16">
         <v>4</v>
       </c>
       <c r="C77" s="9" t="s">
@@ -1948,10 +2004,10 @@
       <c r="E77" s="3"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="9" t="s">
+      <c r="A78" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="B78" s="9">
+      <c r="B78" s="16">
         <v>4</v>
       </c>
       <c r="C78" s="9" t="s">
@@ -1963,10 +2019,10 @@
       <c r="E78" s="3"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="9" t="s">
+      <c r="A79" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="B79" s="9">
+      <c r="B79" s="16">
         <v>4</v>
       </c>
       <c r="C79" s="9" t="s">
@@ -1978,10 +2034,10 @@
       <c r="E79" s="3"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="9" t="s">
+      <c r="A80" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="B80" s="9">
+      <c r="B80" s="16">
         <v>4</v>
       </c>
       <c r="C80" s="9" t="s">
@@ -1993,10 +2049,10 @@
       <c r="E80" s="3"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="9" t="s">
+      <c r="A81" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="B81" s="9">
+      <c r="B81" s="16">
         <v>4</v>
       </c>
       <c r="C81" s="9" t="s">
@@ -2008,10 +2064,10 @@
       <c r="E81" s="3"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="9" t="s">
+      <c r="A82" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="B82" s="9">
+      <c r="B82" s="16">
         <v>4</v>
       </c>
       <c r="C82" s="9" t="s">
@@ -2023,10 +2079,10 @@
       <c r="E82" s="3"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="9" t="s">
+      <c r="A83" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="B83" s="9">
+      <c r="B83" s="16">
         <v>4</v>
       </c>
       <c r="C83" s="9" t="s">
@@ -2038,10 +2094,10 @@
       <c r="E83" s="3"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="9" t="s">
+      <c r="A84" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B84" s="9">
+      <c r="B84" s="16">
         <v>4</v>
       </c>
       <c r="C84" s="9" t="s">
@@ -2053,10 +2109,10 @@
       <c r="E84" s="3"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="9" t="s">
+      <c r="A85" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="B85" s="9">
+      <c r="B85" s="16">
         <v>4</v>
       </c>
       <c r="C85" s="9" t="s">
@@ -2068,10 +2124,10 @@
       <c r="E85" s="3"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="9" t="s">
+      <c r="A86" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="B86" s="9">
+      <c r="B86" s="16">
         <v>4</v>
       </c>
       <c r="C86" s="9" t="s">
@@ -2083,10 +2139,10 @@
       <c r="E86" s="3"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="9" t="s">
+      <c r="A87" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="B87" s="9">
+      <c r="B87" s="16">
         <v>4</v>
       </c>
       <c r="C87" s="9" t="s">
@@ -2098,10 +2154,10 @@
       <c r="E87" s="3"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="9" t="s">
+      <c r="A88" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B88" s="9">
+      <c r="B88" s="16">
         <v>4</v>
       </c>
       <c r="C88" s="9" t="s">
@@ -2113,10 +2169,10 @@
       <c r="E88" s="3"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="9" t="s">
+      <c r="A89" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="B89" s="9">
+      <c r="B89" s="16">
         <v>4</v>
       </c>
       <c r="C89" s="9" t="s">
@@ -2128,10 +2184,10 @@
       <c r="E89" s="3"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="9" t="s">
+      <c r="A90" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B90" s="9">
+      <c r="B90" s="16">
         <v>4</v>
       </c>
       <c r="C90" s="9" t="s">
@@ -2143,10 +2199,10 @@
       <c r="E90" s="3"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="9" t="s">
+      <c r="A91" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B91" s="9">
+      <c r="B91" s="16">
         <v>4</v>
       </c>
       <c r="C91" s="9" t="s">
@@ -2158,10 +2214,10 @@
       <c r="E91" s="3"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="9" t="s">
+      <c r="A92" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="B92" s="9">
+      <c r="B92" s="16">
         <v>4</v>
       </c>
       <c r="C92" s="9" t="s">
@@ -2173,10 +2229,10 @@
       <c r="E92" s="3"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="9" t="s">
+      <c r="A93" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="B93" s="9">
+      <c r="B93" s="16">
         <v>4</v>
       </c>
       <c r="C93" s="9" t="s">
@@ -2188,10 +2244,10 @@
       <c r="E93" s="3"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="9" t="s">
+      <c r="A94" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="B94" s="9">
+      <c r="B94" s="16">
         <v>4</v>
       </c>
       <c r="C94" s="9" t="s">
@@ -2203,10 +2259,10 @@
       <c r="E94" s="3"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="9" t="s">
+      <c r="A95" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="B95" s="9">
+      <c r="B95" s="16">
         <v>4</v>
       </c>
       <c r="C95" s="9" t="s">
@@ -2218,10 +2274,10 @@
       <c r="E95" s="3"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="9" t="s">
+      <c r="A96" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="B96" s="9">
+      <c r="B96" s="16">
         <v>4</v>
       </c>
       <c r="C96" s="9" t="s">
@@ -2233,10 +2289,10 @@
       <c r="E96" s="3"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="9" t="s">
+      <c r="A97" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="B97" s="9">
+      <c r="B97" s="16">
         <v>4</v>
       </c>
       <c r="C97" s="9" t="s">
@@ -2248,10 +2304,10 @@
       <c r="E97" s="3"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="9" t="s">
+      <c r="A98" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="B98" s="9">
+      <c r="B98" s="16">
         <v>4</v>
       </c>
       <c r="C98" s="9" t="s">
@@ -2263,10 +2319,10 @@
       <c r="E98" s="3"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="9" t="s">
+      <c r="A99" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="B99" s="9">
+      <c r="B99" s="16">
         <v>4</v>
       </c>
       <c r="C99" s="9" t="s">
@@ -2278,10 +2334,10 @@
       <c r="E99" s="3"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="9" t="s">
+      <c r="A100" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="B100" s="9">
+      <c r="B100" s="16">
         <v>4</v>
       </c>
       <c r="C100" s="9" t="s">
@@ -2293,10 +2349,10 @@
       <c r="E100" s="3"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="9" t="s">
+      <c r="A101" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="B101" s="9">
+      <c r="B101" s="16">
         <v>4</v>
       </c>
       <c r="C101" s="9" t="s">
@@ -2308,10 +2364,10 @@
       <c r="E101" s="3"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="9" t="s">
+      <c r="A102" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="B102" s="9">
+      <c r="B102" s="16">
         <v>4</v>
       </c>
       <c r="C102" s="9" t="s">
@@ -2323,10 +2379,10 @@
       <c r="E102" s="3"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="9" t="s">
+      <c r="A103" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="B103" s="9">
+      <c r="B103" s="16">
         <v>64</v>
       </c>
       <c r="C103" s="9" t="s">
@@ -2338,10 +2394,10 @@
       <c r="E103" s="3"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="9" t="s">
+      <c r="A104" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="B104" s="9">
+      <c r="B104" s="16">
         <v>40</v>
       </c>
       <c r="C104" s="9" t="s">
@@ -2353,10 +2409,10 @@
       <c r="E104" s="3"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="9" t="s">
+      <c r="A105" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="B105" s="9">
+      <c r="B105" s="16">
         <v>32</v>
       </c>
       <c r="C105" s="9" t="s">
@@ -2368,10 +2424,10 @@
       <c r="E105" s="3"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="10" t="s">
+      <c r="A106" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="B106" s="10">
+      <c r="B106" s="17">
         <v>28</v>
       </c>
       <c r="C106" s="10" t="s">
@@ -2383,10 +2439,10 @@
       <c r="E106" s="4"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="10" t="s">
+      <c r="A107" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="B107" s="10">
+      <c r="B107" s="18">
         <v>24</v>
       </c>
       <c r="C107" s="10" t="s">
@@ -2398,10 +2454,10 @@
       <c r="E107" s="4"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="10" t="s">
+      <c r="A108" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="B108" s="10">
+      <c r="B108" s="18">
         <v>20</v>
       </c>
       <c r="C108" s="10" t="s">
@@ -2413,10 +2469,10 @@
       <c r="E108" s="4"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="10" t="s">
+      <c r="A109" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="B109" s="10">
+      <c r="B109" s="18">
         <v>16</v>
       </c>
       <c r="C109" s="10" t="s">
@@ -2428,10 +2484,10 @@
       <c r="E109" s="4"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="10" t="s">
+      <c r="A110" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="B110" s="10">
+      <c r="B110" s="18">
         <v>16</v>
       </c>
       <c r="C110" s="10" t="s">
@@ -2443,10 +2499,10 @@
       <c r="E110" s="4"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="10" t="s">
+      <c r="A111" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="B111" s="10">
+      <c r="B111" s="18">
         <v>12</v>
       </c>
       <c r="C111" s="10" t="s">
@@ -2458,10 +2514,10 @@
       <c r="E111" s="4"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="10" t="s">
+      <c r="A112" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="B112" s="10">
+      <c r="B112" s="18">
         <v>8</v>
       </c>
       <c r="C112" s="10" t="s">
@@ -2473,10 +2529,10 @@
       <c r="E112" s="4"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="10" t="s">
+      <c r="A113" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="B113" s="10">
+      <c r="B113" s="18">
         <v>8</v>
       </c>
       <c r="C113" s="10" t="s">
@@ -2488,10 +2544,10 @@
       <c r="E113" s="4"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="10" t="s">
+      <c r="A114" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="B114" s="10">
+      <c r="B114" s="18">
         <v>8</v>
       </c>
       <c r="C114" s="10" t="s">
@@ -2503,10 +2559,10 @@
       <c r="E114" s="4"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="10" t="s">
+      <c r="A115" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="B115" s="10">
+      <c r="B115" s="18">
         <v>8</v>
       </c>
       <c r="C115" s="10" t="s">
@@ -2518,10 +2574,10 @@
       <c r="E115" s="4"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="11" t="s">
+      <c r="A116" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="B116" s="11">
+      <c r="B116" s="19">
         <v>4</v>
       </c>
       <c r="C116" s="11" t="s">
